--- a/test_data/MyAGVPro.xlsx
+++ b/test_data/MyAGVPro.xlsx
@@ -4,14 +4,45 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11870"/>
+    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="19" activeTab="23"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
-    <sheet name="get_modified_version" sheetId="2" r:id="rId2"/>
+    <sheet name="get_modify_version" sheetId="2" r:id="rId2"/>
     <sheet name="get_robot_status" sheetId="3" r:id="rId3"/>
     <sheet name="power_on" sheetId="4" r:id="rId4"/>
     <sheet name="power_off" sheetId="5" r:id="rId5"/>
+    <sheet name="is_power_on" sheetId="6" r:id="rId6"/>
+    <sheet name="move_forward" sheetId="7" r:id="rId7"/>
+    <sheet name="move_backward" sheetId="8" r:id="rId8"/>
+    <sheet name="move_right_lateral" sheetId="9" r:id="rId9"/>
+    <sheet name="move_left_lateral" sheetId="10" r:id="rId10"/>
+    <sheet name="turn_left" sheetId="11" r:id="rId11"/>
+    <sheet name="turn_right" sheetId="12" r:id="rId12"/>
+    <sheet name="stop" sheetId="13" r:id="rId13"/>
+    <sheet name="set_auto_report_state" sheetId="14" r:id="rId14"/>
+    <sheet name="get_auto_report_state" sheetId="15" r:id="rId15"/>
+    <sheet name="get_auto_report_message" sheetId="16" r:id="rId16"/>
+    <sheet name="set_motor_enable" sheetId="17" r:id="rId17"/>
+    <sheet name="get_motor_status" sheetId="18" r:id="rId18"/>
+    <sheet name="get_motor_temps" sheetId="19" r:id="rId19"/>
+    <sheet name="get_motor_speeds" sheetId="20" r:id="rId20"/>
+    <sheet name="get_motor_torques" sheetId="21" r:id="rId21"/>
+    <sheet name="get_motor_enable_status" sheetId="22" r:id="rId22"/>
+    <sheet name="get_motor_loss_count" sheetId="23" r:id="rId23"/>
+    <sheet name="set_communication_state" sheetId="24" r:id="rId24"/>
+    <sheet name="get_communication_state" sheetId="25" r:id="rId25"/>
+    <sheet name="set_led_color" sheetId="26" r:id="rId26"/>
+    <sheet name="set_led_mode" sheetId="27" r:id="rId27"/>
+    <sheet name="set_handle_control_state" sheetId="28" r:id="rId28"/>
+    <sheet name="get_handle_control_state" sheetId="29" r:id="rId29"/>
+    <sheet name="set_pin_output" sheetId="30" r:id="rId30"/>
+    <sheet name="get_pin_input" sheetId="31" r:id="rId31"/>
+    <sheet name="get_estop_state" sheetId="32" r:id="rId32"/>
+    <sheet name="get_wifi_account" sheetId="33" r:id="rId33"/>
+    <sheet name="get_wifi_ip_port" sheetId="34" r:id="rId34"/>
+    <sheet name="get_bluetooth_uuid" sheetId="35" r:id="rId35"/>
+    <sheet name="get_bluetooth_address" sheetId="36" r:id="rId36"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="264">
   <si>
     <t>ID</t>
   </si>
@@ -63,7 +94,768 @@
     <t>正确获取修正版本号</t>
   </si>
   <si>
-    <t>get_modified_version</t>
+    <t>get_modify_version</t>
+  </si>
+  <si>
+    <t>读取机器状态（上电）</t>
+  </si>
+  <si>
+    <t>get_robot_status</t>
+  </si>
+  <si>
+    <t>([0, 0, 0, 0, 0, 0, 0, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>读取机器状态（下电）</t>
+  </si>
+  <si>
+    <t>([1, 1, 0, 0, 0, 0, 0, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>读取机器状态（拍急停）</t>
+  </si>
+  <si>
+    <t>exception</t>
+  </si>
+  <si>
+    <t>读取机器状态（触发防撞条1）</t>
+  </si>
+  <si>
+    <t>([1, 1, 1, 0, 0, 0, 0, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>读取机器状态（触发防撞2）</t>
+  </si>
+  <si>
+    <t>([1, 1, 0, 1, 0, 0, 0, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>读取机器状态（断开1号电机连接）</t>
+  </si>
+  <si>
+    <t>([0, 0, 0, 0, 1, 0, 0, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>Disconnect</t>
+  </si>
+  <si>
+    <t>读取机器状态（断开2号电机连接）</t>
+  </si>
+  <si>
+    <t>([0, 0, 0, 0, 0, 1, 0, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>读取机器状态（断开3号电机连接）</t>
+  </si>
+  <si>
+    <t>([0, 0, 0, 0, 0, 0, 1, 0], 23.3)</t>
+  </si>
+  <si>
+    <t>读取机器状态（断开4号电机连接）</t>
+  </si>
+  <si>
+    <t>([0, 0, 0, 0, 0, 0, 0, 1], 23.3)</t>
+  </si>
+  <si>
+    <t>上电（上电时）</t>
+  </si>
+  <si>
+    <t>power_on</t>
+  </si>
+  <si>
+    <t>上电（下电时）</t>
+  </si>
+  <si>
+    <t>上电（拍下急停时）</t>
+  </si>
+  <si>
+    <t>下电（上电时）</t>
+  </si>
+  <si>
+    <t>power_off</t>
+  </si>
+  <si>
+    <t>下电（下电时）</t>
+  </si>
+  <si>
+    <t>下电（拍下急停时）</t>
+  </si>
+  <si>
+    <t>主控是否上电（上电）</t>
+  </si>
+  <si>
+    <t>is_power_on</t>
+  </si>
+  <si>
+    <t>主控是否上电（下电）</t>
+  </si>
+  <si>
+    <t>主控是否上电（拍下急停）</t>
+  </si>
+  <si>
+    <t>小车向前（上电）</t>
+  </si>
+  <si>
+    <t>move_forward</t>
+  </si>
+  <si>
+    <t>小车向前（下电）</t>
+  </si>
+  <si>
+    <t>小车向前（速度超限）</t>
+  </si>
+  <si>
+    <t>小车向前（有效位超限）</t>
+  </si>
+  <si>
+    <t>小车向前（参数类型超限）</t>
+  </si>
+  <si>
+    <t>"1"</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>{1}</t>
+  </si>
+  <si>
+    <t>小车向后（上电）</t>
+  </si>
+  <si>
+    <t>move_backward</t>
+  </si>
+  <si>
+    <t>小车向后（下电）</t>
+  </si>
+  <si>
+    <t>小车向后（速度超限）</t>
+  </si>
+  <si>
+    <t>小车向后（有效位超限）</t>
+  </si>
+  <si>
+    <t>小车向后（参数类型超限）</t>
+  </si>
+  <si>
+    <t>小车向右平移（上电）</t>
+  </si>
+  <si>
+    <t>move_right_lateral</t>
+  </si>
+  <si>
+    <t>小车向右平移（下电）</t>
+  </si>
+  <si>
+    <t>小车向右平移（速度超限）</t>
+  </si>
+  <si>
+    <t>小车向右平移（有效位超限）</t>
+  </si>
+  <si>
+    <t>小车向右平移（参数类型超限）</t>
+  </si>
+  <si>
+    <t>小车向左平移（上电）</t>
+  </si>
+  <si>
+    <t>move_left_lateral</t>
+  </si>
+  <si>
+    <t>小车向左平移（下电）</t>
+  </si>
+  <si>
+    <t>小车向左平移（速度超限）</t>
+  </si>
+  <si>
+    <t>小车向左平移（有效位超限）</t>
+  </si>
+  <si>
+    <t>小车向左平移（参数类型超限）</t>
+  </si>
+  <si>
+    <t>小车向左旋（上电）</t>
+  </si>
+  <si>
+    <t>turn_left</t>
+  </si>
+  <si>
+    <t>小车向左旋（下电）</t>
+  </si>
+  <si>
+    <t>小车向左旋（有效位超限）</t>
+  </si>
+  <si>
+    <t>小车向左旋（参数类型超限）</t>
+  </si>
+  <si>
+    <t>小车向右旋（上电）</t>
+  </si>
+  <si>
+    <t>turn_right</t>
+  </si>
+  <si>
+    <t>小车向右旋（下电）</t>
+  </si>
+  <si>
+    <t>小车向右旋（有效位超限）</t>
+  </si>
+  <si>
+    <t>小车向右旋（参数类型超限）</t>
+  </si>
+  <si>
+    <t>小车停止运动（向前）</t>
+  </si>
+  <si>
+    <t>stop</t>
+  </si>
+  <si>
+    <t>小车停止运动（向后）</t>
+  </si>
+  <si>
+    <t>小车停止运动（左平移）</t>
+  </si>
+  <si>
+    <t>小车停止运动（右平移）</t>
+  </si>
+  <si>
+    <t>小车停止运动（左旋）</t>
+  </si>
+  <si>
+    <t>小车停止运动（右旋）</t>
+  </si>
+  <si>
+    <t>小车停止运动（下电）</t>
+  </si>
+  <si>
+    <t>设置自动上发状态（状态1）</t>
+  </si>
+  <si>
+    <t>set_auto_report_state</t>
+  </si>
+  <si>
+    <t>设置自动上发状态（状态0）</t>
+  </si>
+  <si>
+    <t>设置自动上发状态（下电）</t>
+  </si>
+  <si>
+    <t>设置自动上发状态（参数超限）</t>
+  </si>
+  <si>
+    <t>设置自动上发状态（参数类型超限）</t>
+  </si>
+  <si>
+    <t>设置自动上发状态（掉电重启）</t>
+  </si>
+  <si>
+    <t>save_or_not</t>
+  </si>
+  <si>
+    <t>读取自动上发状态（状态1）</t>
+  </si>
+  <si>
+    <t>get_auto_report_state</t>
+  </si>
+  <si>
+    <t>读取自动上发状态（状态0）</t>
+  </si>
+  <si>
+    <t>读取自动上发状态（下电）</t>
+  </si>
+  <si>
+    <t>list_len</t>
+  </si>
+  <si>
+    <t>读取自动上发内容（状态1）</t>
+  </si>
+  <si>
+    <t>get_auto_report_message</t>
+  </si>
+  <si>
+    <t>[0.0, 0.0, 0.0, 0, 0, 23.0, 0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
+  </si>
+  <si>
+    <t>读取自动上发内容（状态0）</t>
+  </si>
+  <si>
+    <t>读取自动上发内容（下电）</t>
+  </si>
+  <si>
+    <t>motor_id</t>
+  </si>
+  <si>
+    <t>state</t>
+  </si>
+  <si>
+    <t>电机使能（电机1失能）</t>
+  </si>
+  <si>
+    <t>set_motor_enable</t>
+  </si>
+  <si>
+    <t>电机使能（电机1使能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机2失能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机2使能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机3失能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机3使能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机4失能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机4使能）</t>
+  </si>
+  <si>
+    <t>电机使能（所有电机失能）</t>
+  </si>
+  <si>
+    <t>电机使能（所有电机使能）</t>
+  </si>
+  <si>
+    <t>电机使能（电机ID超限）</t>
+  </si>
+  <si>
+    <t>exception1</t>
+  </si>
+  <si>
+    <t>电机使能（电机ID类型超限）</t>
+  </si>
+  <si>
+    <t>电机使能（状态超限）</t>
+  </si>
+  <si>
+    <t>exception2</t>
+  </si>
+  <si>
+    <t>电机使能（状态类型超限）</t>
+  </si>
+  <si>
+    <t>电机使能（下电）</t>
+  </si>
+  <si>
+    <t>读取所有电机状态（上电）</t>
+  </si>
+  <si>
+    <t>get_motor_status</t>
+  </si>
+  <si>
+    <t>[0, 0, 0, 0]</t>
+  </si>
+  <si>
+    <t>读取所有电机状态（下电）</t>
+  </si>
+  <si>
+    <t>speed</t>
+  </si>
+  <si>
+    <t>range_limitation</t>
+  </si>
+  <si>
+    <t>读取所有电机温度（速度0.5运动）</t>
+  </si>
+  <si>
+    <t>get_motor_temps</t>
+  </si>
+  <si>
+    <t>[30, 30, 30, 30]</t>
+  </si>
+  <si>
+    <t>读取所有电机温度（速度1.0运动）</t>
+  </si>
+  <si>
+    <t>读取所有电机温度（速度1.5运动）</t>
+  </si>
+  <si>
+    <t>读取所有电机温度（下电）</t>
+  </si>
+  <si>
+    <t>读取所有电机转速（速度0.5运动）</t>
+  </si>
+  <si>
+    <t>get_motor_speeds</t>
+  </si>
+  <si>
+    <t>读取所有电机转速（速度1.0运动）</t>
+  </si>
+  <si>
+    <t>读取所有电机转速（速度1.5运动）</t>
+  </si>
+  <si>
+    <t>读取所有电机转速（下电）</t>
+  </si>
+  <si>
+    <t>读取所有电机力矩（速度0.5运动）</t>
+  </si>
+  <si>
+    <t>get_motor_torques</t>
+  </si>
+  <si>
+    <t>读取所有电机力矩（速度1.0运动）</t>
+  </si>
+  <si>
+    <t>读取所有电机力矩（速度1.5运动）</t>
+  </si>
+  <si>
+    <t>读取所有电机力矩（下电）</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机1失能）</t>
+  </si>
+  <si>
+    <t>get_motor_enable_status</t>
+  </si>
+  <si>
+    <t>[0, 1, 1, 1]</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机1使能）</t>
+  </si>
+  <si>
+    <t>[1, 1, 1, 1]</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机2失能）</t>
+  </si>
+  <si>
+    <t>[1, 0, 1, 1]</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机2使能）</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机3失能）</t>
+  </si>
+  <si>
+    <t>[1, 1, 0, 1]</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机3使能）</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机4失能）</t>
+  </si>
+  <si>
+    <t>[1, 1, 1, 0]</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（电机4使能）</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（所有电机失能）</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（所有电机使能）</t>
+  </si>
+  <si>
+    <t>读取所有电机使能情况（下电）</t>
+  </si>
+  <si>
+    <t>查看电机丢包次数（上电）</t>
+  </si>
+  <si>
+    <t>get_motor_loss_count</t>
+  </si>
+  <si>
+    <t>查看电机丢包次数（下电）</t>
+  </si>
+  <si>
+    <t>expect_data_get</t>
+  </si>
+  <si>
+    <t>设置通信模式（模式1）</t>
+  </si>
+  <si>
+    <t>set_communication_state</t>
+  </si>
+  <si>
+    <t>设置通信模式（模式2）</t>
+  </si>
+  <si>
+    <t>设置通信模式（模式3）</t>
+  </si>
+  <si>
+    <t>设置通信模式（下电）</t>
+  </si>
+  <si>
+    <t>设置通信模式（参数超限）</t>
+  </si>
+  <si>
+    <t>设置通信模式（参数类型超限）</t>
+  </si>
+  <si>
+    <t>(1,)</t>
+  </si>
+  <si>
+    <t>读取通信模式（上电）</t>
+  </si>
+  <si>
+    <t>get_communication_state</t>
+  </si>
+  <si>
+    <t>读取通信模式（下电）</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>brightness</t>
+  </si>
+  <si>
+    <t>DIY灯带（左灯带红亮度100）</t>
+  </si>
+  <si>
+    <t>set_led_color</t>
+  </si>
+  <si>
+    <t>(255,0,0)</t>
+  </si>
+  <si>
+    <t>DIY灯带（左灯带绿亮度100）</t>
+  </si>
+  <si>
+    <t>(0,255,0)</t>
+  </si>
+  <si>
+    <t>DIY灯带（左灯带蓝亮度100）</t>
+  </si>
+  <si>
+    <t>(0,0,255)</t>
+  </si>
+  <si>
+    <t>DIY灯带（左灯带红亮度255）</t>
+  </si>
+  <si>
+    <t>DIY灯带（左灯带绿亮度255）</t>
+  </si>
+  <si>
+    <t>DIY灯带（左灯带蓝亮度255）</t>
+  </si>
+  <si>
+    <t>DIY灯带（右灯带红亮度100）</t>
+  </si>
+  <si>
+    <t>DIY灯带（右灯带绿亮度100）</t>
+  </si>
+  <si>
+    <t>DIY灯带（右灯带蓝亮度100）</t>
+  </si>
+  <si>
+    <t>DIY灯带（右灯带红亮度255）</t>
+  </si>
+  <si>
+    <t>DIY灯带（右灯带绿亮度255）</t>
+  </si>
+  <si>
+    <t>DIY灯带（右灯带蓝亮度255）</t>
+  </si>
+  <si>
+    <t>DIY灯带（下电）</t>
+  </si>
+  <si>
+    <t>DIY灯带（position
+参数超限）</t>
+  </si>
+  <si>
+    <t>DIY灯带（position
+参数类型超限）</t>
+  </si>
+  <si>
+    <t>"0"</t>
+  </si>
+  <si>
+    <t>(0,)</t>
+  </si>
+  <si>
+    <t>[0]</t>
+  </si>
+  <si>
+    <t>{0}</t>
+  </si>
+  <si>
+    <t>DIY灯带（color参数超限）</t>
+  </si>
+  <si>
+    <t>(-1,0,0)</t>
+  </si>
+  <si>
+    <t>(256,0,0)</t>
+  </si>
+  <si>
+    <t>(0,-1,0)</t>
+  </si>
+  <si>
+    <t>(0,256,0)</t>
+  </si>
+  <si>
+    <t>(0,0,-1)</t>
+  </si>
+  <si>
+    <t>(0,0,256)</t>
+  </si>
+  <si>
+    <t>DIY灯带（color参数长度超限）</t>
+  </si>
+  <si>
+    <t>(0,255)</t>
+  </si>
+  <si>
+    <t>(0,255,0,0)</t>
+  </si>
+  <si>
+    <t>DIY灯带（color参数类型超限）</t>
+  </si>
+  <si>
+    <t>"(0,255,0)"</t>
+  </si>
+  <si>
+    <t>[0,255,0]</t>
+  </si>
+  <si>
+    <t>{0,255,0}</t>
+  </si>
+  <si>
+    <t>DIY灯带（brightness参数超限）</t>
+  </si>
+  <si>
+    <t>exception3</t>
+  </si>
+  <si>
+    <t>DIY灯带（brightness参数类型超限）</t>
+  </si>
+  <si>
+    <t>"100"</t>
+  </si>
+  <si>
+    <t>(100,)</t>
+  </si>
+  <si>
+    <t>[100]</t>
+  </si>
+  <si>
+    <t>{100}</t>
+  </si>
+  <si>
+    <t>mode</t>
+  </si>
+  <si>
+    <t>设置灯带模式（模式0）</t>
+  </si>
+  <si>
+    <t>set_led_mode</t>
+  </si>
+  <si>
+    <t>normal1</t>
+  </si>
+  <si>
+    <t>设置灯带模式（模式1）</t>
+  </si>
+  <si>
+    <t>normal2</t>
+  </si>
+  <si>
+    <t>设置灯带模式（下电）</t>
+  </si>
+  <si>
+    <t>设置灯带模式（参数超限）</t>
+  </si>
+  <si>
+    <t>设置灯带模式（参数类型超限）</t>
+  </si>
+  <si>
+    <t>设置手柄控制开关状态（模式0）</t>
+  </si>
+  <si>
+    <t>set_handle_control_state</t>
+  </si>
+  <si>
+    <t>设置手柄控制开关状态（模式1）</t>
+  </si>
+  <si>
+    <t>设置手柄控制开关状态（下电）</t>
+  </si>
+  <si>
+    <t>设置手柄控制开关状态（参数超限）</t>
+  </si>
+  <si>
+    <t>设置手柄控制开关状态（参数类型超限）</t>
+  </si>
+  <si>
+    <t>读取手柄控制开关状态（模式0）</t>
+  </si>
+  <si>
+    <t>get_handle_control_state</t>
+  </si>
+  <si>
+    <t>读取手柄控制开关状态（模式1）</t>
+  </si>
+  <si>
+    <t>读取手柄控制开关状态（下电）</t>
+  </si>
+  <si>
+    <t>读取急停按钮状态（急停按下）</t>
+  </si>
+  <si>
+    <t>get_estop_state</t>
+  </si>
+  <si>
+    <t>读取急停按钮状态（急停松开）</t>
+  </si>
+  <si>
+    <t>读取WiFi账号密码（上电）</t>
+  </si>
+  <si>
+    <t>get_wifi_account</t>
+  </si>
+  <si>
+    <t>('ElephantAGVPro-AP2.4G', 'elephant')</t>
+  </si>
+  <si>
+    <t>读取WiFi账号密码（下电）</t>
+  </si>
+  <si>
+    <t>读取WiFi-ip、端口号（上电）</t>
+  </si>
+  <si>
+    <t>get_wifi_ip_port</t>
+  </si>
+  <si>
+    <t>('192.168.4.1', 9000)</t>
+  </si>
+  <si>
+    <t>读取WiFi-ip、端口号（下电）</t>
+  </si>
+  <si>
+    <t>读取蓝牙名称、uuid（上电）</t>
+  </si>
+  <si>
+    <t>get_bluetooth_uuid</t>
+  </si>
+  <si>
+    <t>('BLE-Elephant-AGVPro', '9a95aa42-ba2f-4bd0-8296-73c0c89c0871', 'd886e992-a18a-4dc3-9362-2fc15b4b576a')</t>
+  </si>
+  <si>
+    <t>读取蓝牙名称、uuid（下电）</t>
+  </si>
+  <si>
+    <t>读取蓝牙地址（上电）</t>
+  </si>
+  <si>
+    <t>"00:00:00:00:00:00"</t>
+  </si>
+  <si>
+    <t>读取蓝牙地址（下电）</t>
   </si>
 </sst>
 </file>
@@ -680,7 +1472,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -693,10 +1485,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1047,9 +1848,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="5">
-        <v>1.2</v>
-      </c>
+      <c r="E2" s="7"/>
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1057,6 +1856,1716 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4">
+        <v>0.009</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5">
+        <v>1.51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>0.111</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4">
+        <v>0.111</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4">
+        <v>0.111</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="70" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F2" s="3">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:7">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:7">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:7">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10">
+        <v>254</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11">
+        <v>254</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:7">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:7">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:7">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:7">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:7">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" ht="28" spans="1:7">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>-1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:7">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:7">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:7">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:7">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22">
+        <v>254</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:8">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="2">
+        <v>50</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" s="3">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:8">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>50</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="3">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:8">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>50</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:8">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1101,9 +3610,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="4">
-        <v>5</v>
-      </c>
+      <c r="E2" s="8"/>
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1115,14 +3622,3002 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="3">
+        <v>4</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:7">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:7">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="42" spans="1:7">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D10">
+        <v>254</v>
+      </c>
+      <c r="E10" s="2">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="42" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D11">
+        <v>254</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" ht="28" spans="1:7">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D12">
+        <v>254</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="3">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
+  <cols>
+    <col min="2" max="7" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:7">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:7">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:7">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:7">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:7">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:7">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H37"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <cols>
+    <col min="2" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:8">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F2" s="2">
+        <v>100</v>
+      </c>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:8">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="2">
+        <v>100</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:8">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F4" s="2">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:8">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F5" s="2">
+        <v>255</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:8">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F6" s="2">
+        <v>255</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="28" spans="1:8">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F7" s="2">
+        <v>255</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="28" spans="1:8">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="6">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F8" s="2">
+        <v>100</v>
+      </c>
+      <c r="G8" s="2">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="28" spans="1:8">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="6">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="2">
+        <v>100</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="28" spans="1:8">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F10" s="2">
+        <v>100</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" customFormat="1" ht="28" spans="1:8">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F11" s="2">
+        <v>255</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:8">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="6">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F12" s="2">
+        <v>255</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:8">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D13" s="6">
+        <v>1</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="2">
+        <v>255</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F14" s="2">
+        <v>100</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:8">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15">
+        <v>-1</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F15" s="2">
+        <v>100</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:8">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F16" s="2">
+        <v>100</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" ht="28" spans="1:8">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="2">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" ht="28" spans="1:8">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F18" s="2">
+        <v>100</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" ht="28" spans="1:8">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F19" s="2">
+        <v>100</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" ht="28" spans="1:8">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F20" s="2">
+        <v>100</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:8">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F21">
+        <v>100</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:8">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F22">
+        <v>100</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:8">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" ht="28" spans="1:8">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F24">
+        <v>100</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" ht="28" spans="1:8">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F25">
+        <v>100</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" ht="28" spans="1:8">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" ht="28" spans="1:8">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F27">
+        <v>100</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" ht="28" spans="1:8">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F28">
+        <v>100</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" ht="28" spans="1:8">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D29">
+        <v>0</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" ht="28" spans="1:8">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F30">
+        <v>100</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" ht="28" spans="1:8">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D31">
+        <v>0</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F31">
+        <v>100</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" ht="42" spans="1:8">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" s="2">
+        <v>0</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F32">
+        <v>-1</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="33" ht="42" spans="1:8">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="2">
+        <v>0</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33">
+        <v>256</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="34" ht="42" spans="1:8">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="2">
+        <v>0</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="35" ht="42" spans="1:8">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="2">
+        <v>0</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" ht="42" spans="1:8">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="2">
+        <v>0</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" ht="42" spans="1:8">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D37" s="2">
+        <v>0</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>221</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" ht="42" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" customFormat="1" ht="42" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="42" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" customFormat="1" ht="42" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="42" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="112" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1130,9 +6625,85 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1141,9 +6712,696 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="E3"/>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4">
+        <v>0.009</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5">
+        <v>1.51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6">
+        <v>0.111</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4">
+        <v>0.009</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5">
+        <v>1.51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6">
+        <v>0.111</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
+  <cols>
+    <col min="2" max="6" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" ht="28" spans="1:6">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" ht="28" spans="1:6">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3">
+        <v>0.1</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" customFormat="1" ht="28" spans="1:6">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4">
+        <v>0.009</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" customFormat="1" ht="28" spans="1:6">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5">
+        <v>1.51</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="1" ht="28" spans="1:6">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6">
+        <v>0.111</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:6">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:6">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/test_data/MyAGVPro.xlsx
+++ b/test_data/MyAGVPro.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="19" activeTab="23"/>
+    <workbookView windowWidth="24750" windowHeight="11870" firstSheet="25" activeTab="30"/>
   </bookViews>
   <sheets>
     <sheet name="get_system_version" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="299">
   <si>
     <t>ID</t>
   </si>
@@ -220,6 +220,9 @@
     <t>{1}</t>
   </si>
   <si>
+    <t>(1,)</t>
+  </si>
+  <si>
     <t>小车向后（上电）</t>
   </si>
   <si>
@@ -590,9 +593,6 @@
   </si>
   <si>
     <t>设置通信模式（参数类型超限）</t>
-  </si>
-  <si>
-    <t>(1,)</t>
   </si>
   <si>
     <t>读取通信模式（上电）</t>
@@ -802,6 +802,111 @@
   </si>
   <si>
     <t>读取手柄控制开关状态（下电）</t>
+  </si>
+  <si>
+    <t>pin</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚1状态1）</t>
+  </si>
+  <si>
+    <t>set_pin_output</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚1状态0）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚2状态1）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚2状态0）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚3状态1）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚3状态0）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚4状态1）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚4状态0）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚5状态1）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚5状态0）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚6状态1）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（引脚6状态0）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（下电）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（pin参数超限）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（pin参数类型超限）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（state参数超限）</t>
+  </si>
+  <si>
+    <t>设置输出引脚状态（state参数类型超限）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚1状态1）</t>
+  </si>
+  <si>
+    <t>get_pin_input</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚1状态0）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚2状态1）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚2状态0）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚3状态1）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚3状态0）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚4状态1）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚4状态0）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚5状态1）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚5状态0）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚6状态1）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（设置引脚6状态0）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（下电）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（pin参数超限）</t>
+  </si>
+  <si>
+    <t>读取输入引脚状态（pin参数类型超限）</t>
   </si>
   <si>
     <t>读取急停按钮状态（急停按下）</t>
@@ -869,13 +974,19 @@
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -1342,16 +1453,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -1360,119 +1468,122 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1485,10 +1596,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1848,7 +1962,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="7"/>
+      <c r="E2" s="8"/>
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
@@ -1863,7 +1977,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
@@ -1894,10 +2008,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2">
         <v>0.1</v>
@@ -1914,10 +2028,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>65</v>
       </c>
       <c r="D3">
         <v>0.1</v>
@@ -1931,10 +2045,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4">
         <v>0.009</v>
@@ -1948,10 +2062,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D5">
         <v>1.51</v>
@@ -1965,10 +2079,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6">
         <v>0.111</v>
@@ -1982,10 +2096,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>49</v>
@@ -1999,10 +2113,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>50</v>
@@ -2016,15 +2130,32 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2037,8 +2168,8 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -2068,10 +2199,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D2" s="2">
         <v>0.5</v>
@@ -2088,10 +2219,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>71</v>
       </c>
       <c r="D3" s="2">
         <v>0.5</v>
@@ -2105,10 +2236,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D4">
         <v>0.111</v>
@@ -2122,10 +2253,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>49</v>
@@ -2139,10 +2270,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>50</v>
@@ -2156,15 +2287,32 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2177,8 +2325,8 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="5"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
@@ -2208,10 +2356,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" s="2">
         <v>0.5</v>
@@ -2228,10 +2376,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>77</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>76</v>
       </c>
       <c r="D3" s="2">
         <v>0.5</v>
@@ -2245,10 +2393,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D4">
         <v>0.111</v>
@@ -2262,10 +2410,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>49</v>
@@ -2279,10 +2427,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>50</v>
@@ -2296,15 +2444,32 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:6">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2348,10 +2513,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D2" s="2">
         <v>0.5</v>
@@ -2368,10 +2533,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="D3" s="2">
         <v>0.5</v>
@@ -2388,10 +2553,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2">
         <v>0.5</v>
@@ -2408,10 +2573,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D5" s="2">
         <v>0.5</v>
@@ -2428,10 +2593,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D6" s="2">
         <v>0.5</v>
@@ -2448,10 +2613,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D7" s="2">
         <v>0.5</v>
@@ -2468,10 +2633,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>36</v>
@@ -2486,7 +2651,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
@@ -2517,10 +2682,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2537,10 +2702,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2557,10 +2722,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2575,10 +2740,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D5">
         <v>-1</v>
@@ -2592,10 +2757,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -2609,10 +2774,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>49</v>
@@ -2626,10 +2791,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>50</v>
@@ -2643,10 +2808,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>51</v>
@@ -2663,16 +2828,33 @@
         <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="2">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:6">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>95</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2715,10 +2897,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2735,10 +2917,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2755,10 +2937,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D4" s="2">
         <v>0</v>
@@ -2799,7 +2981,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -2810,16 +2992,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F2" s="3">
         <v>16</v>
@@ -2833,10 +3015,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
@@ -2852,10 +3034,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D4" s="2"/>
       <c r="F4" s="3"/>
@@ -2872,7 +3054,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="2" max="7" width="18" customWidth="1"/>
@@ -2889,10 +3071,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -2906,10 +3088,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -2929,10 +3111,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -2952,10 +3134,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -2975,10 +3157,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -2998,10 +3180,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -3021,10 +3203,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -3044,10 +3226,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -3067,10 +3249,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -3090,10 +3272,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D10">
         <v>254</v>
@@ -3113,10 +3295,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D11">
         <v>254</v>
@@ -3136,10 +3318,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -3148,7 +3330,7 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" ht="28" spans="1:7">
@@ -3156,10 +3338,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -3168,7 +3350,7 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" ht="28" spans="1:7">
@@ -3176,10 +3358,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>49</v>
@@ -3188,7 +3370,7 @@
         <v>1</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" ht="28" spans="1:7">
@@ -3196,10 +3378,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>50</v>
@@ -3208,7 +3390,7 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:7">
@@ -3216,10 +3398,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>51</v>
@@ -3228,7 +3410,7 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:7">
@@ -3239,16 +3421,16 @@
         <v>122</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
+        <v>110</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:7">
@@ -3256,19 +3438,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D18">
         <v>1</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" ht="28" spans="1:7">
@@ -3276,19 +3458,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="20" ht="28" spans="1:7">
@@ -3296,19 +3478,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="21" ht="28" spans="1:7">
@@ -3316,22 +3498,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
+    </row>
+    <row r="22" ht="28" spans="1:7">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -3339,15 +3521,55 @@
         <v>125</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" ht="28" spans="1:7">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D24">
         <v>254</v>
       </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3383,7 +3605,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -3394,14 +3616,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="3">
         <v>4</v>
@@ -3415,10 +3637,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3453,16 +3675,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>5</v>
@@ -3473,10 +3695,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D2" s="2">
         <v>0.5</v>
@@ -3485,7 +3707,7 @@
         <v>50</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G2" s="3">
         <v>4</v>
@@ -3499,10 +3721,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3511,7 +3733,7 @@
         <v>50</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G3" s="3">
         <v>4</v>
@@ -3525,10 +3747,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D4" s="2">
         <v>1.5</v>
@@ -3537,7 +3759,7 @@
         <v>50</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G4" s="3">
         <v>4</v>
@@ -3551,10 +3773,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -3610,7 +3832,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="8"/>
+      <c r="E2" s="9"/>
       <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
@@ -3642,13 +3864,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -3659,16 +3881,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D2" s="2">
         <v>0.5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="3">
         <v>4</v>
@@ -3682,16 +3904,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F3" s="3">
         <v>4</v>
@@ -3705,16 +3927,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="2">
         <v>1.5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F4" s="3">
         <v>4</v>
@@ -3728,10 +3950,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -3766,13 +3988,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -3783,16 +4005,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D2" s="2">
         <v>0.5</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="3">
         <v>4</v>
@@ -3806,16 +4028,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F3" s="3">
         <v>4</v>
@@ -3829,16 +4051,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D4" s="2">
         <v>1.5</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F4" s="3">
         <v>4</v>
@@ -3852,10 +4074,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
@@ -3890,10 +4112,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
@@ -3907,10 +4129,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
@@ -3919,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>8</v>
@@ -3930,10 +4152,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -3942,7 +4164,7 @@
         <v>1</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>8</v>
@@ -3953,10 +4175,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -3965,7 +4187,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>8</v>
@@ -3976,10 +4198,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -3988,7 +4210,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>8</v>
@@ -3999,10 +4221,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -4011,7 +4233,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>8</v>
@@ -4022,10 +4244,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -4034,7 +4256,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>8</v>
@@ -4045,10 +4267,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -4057,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>8</v>
@@ -4068,10 +4290,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -4080,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>8</v>
@@ -4091,10 +4313,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D10">
         <v>254</v>
@@ -4103,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>8</v>
@@ -4114,10 +4336,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D11">
         <v>254</v>
@@ -4126,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>8</v>
@@ -4137,10 +4359,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D12">
         <v>254</v>
@@ -4184,7 +4406,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -4195,14 +4417,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F2" s="3">
         <v>4</v>
@@ -4216,10 +4438,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>166</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -4254,13 +4476,13 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" s="3" t="s">
         <v>5</v>
@@ -4271,10 +4493,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D2" s="2">
         <v>0</v>
@@ -4294,10 +4516,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>170</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
@@ -4317,10 +4539,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D4" s="2">
         <v>2</v>
@@ -4338,10 +4560,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" s="2">
         <v>0</v>
@@ -4357,10 +4579,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D6">
         <v>-1</v>
@@ -4374,10 +4596,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -4391,12 +4613,12 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D8" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
@@ -4408,10 +4630,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>50</v>
@@ -4425,10 +4647,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>51</v>
@@ -4442,13 +4664,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
@@ -4730,7 +4952,7 @@
       <c r="C8" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="7">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="s">
@@ -4756,7 +4978,7 @@
       <c r="C9" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="7">
         <v>1</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -4782,7 +5004,7 @@
       <c r="C10" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="7">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -4808,7 +5030,7 @@
       <c r="C11" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="7">
         <v>1</v>
       </c>
       <c r="E11" s="2" t="s">
@@ -4834,7 +5056,7 @@
       <c r="C12" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="7">
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
@@ -4860,7 +5082,7 @@
       <c r="C13" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="7">
         <v>1</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -4919,7 +5141,7 @@
         <v>100</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" ht="28" spans="1:8">
@@ -4942,7 +5164,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" ht="28" spans="1:8">
@@ -4965,7 +5187,7 @@
         <v>100</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" ht="28" spans="1:8">
@@ -4988,7 +5210,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" ht="28" spans="1:8">
@@ -5011,7 +5233,7 @@
         <v>100</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" ht="28" spans="1:8">
@@ -5034,7 +5256,7 @@
         <v>100</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" ht="28" spans="1:8">
@@ -5057,7 +5279,7 @@
         <v>100</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" ht="28" spans="1:8">
@@ -5080,7 +5302,7 @@
         <v>100</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" ht="28" spans="1:8">
@@ -5103,7 +5325,7 @@
         <v>100</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" ht="28" spans="1:8">
@@ -5126,7 +5348,7 @@
         <v>100</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" ht="28" spans="1:8">
@@ -5149,7 +5371,7 @@
         <v>100</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" ht="28" spans="1:8">
@@ -5172,7 +5394,7 @@
         <v>100</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" ht="28" spans="1:8">
@@ -5195,7 +5417,7 @@
         <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" ht="28" spans="1:8">
@@ -5218,7 +5440,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" ht="28" spans="1:8">
@@ -5241,7 +5463,7 @@
         <v>100</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" ht="28" spans="1:8">
@@ -5264,7 +5486,7 @@
         <v>100</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" ht="28" spans="1:8">
@@ -5287,7 +5509,7 @@
         <v>100</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" ht="42" spans="1:8">
@@ -5565,7 +5787,7 @@
       <c r="C7" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -5617,7 +5839,7 @@
         <v>229</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>17</v>
@@ -5760,7 +5982,7 @@
       <c r="C7" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="F7" s="2" t="s">
@@ -5812,7 +6034,7 @@
         <v>237</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>17</v>
@@ -5951,7 +6173,7 @@
         <v>12</v>
       </c>
       <c r="D2" s="2"/>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -5968,7 +6190,7 @@
       <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
@@ -5985,7 +6207,7 @@
       <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>15</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -6002,7 +6224,7 @@
       <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -6019,7 +6241,7 @@
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -6036,7 +6258,7 @@
       <c r="C7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="8" t="s">
         <v>23</v>
       </c>
       <c r="F7" t="s">
@@ -6053,7 +6275,7 @@
       <c r="C8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F8" t="s">
@@ -6070,7 +6292,7 @@
       <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F9" t="s">
@@ -6087,7 +6309,7 @@
       <c r="C10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F10" t="s">
@@ -6104,13 +6326,13 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6121,65 +6343,552 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28" spans="1:6">
+    <row r="2" ht="28" spans="1:7">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
       <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="28" spans="1:6">
+    <row r="3" customFormat="1" ht="28" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
       <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="28" spans="1:6">
+    <row r="4" customFormat="1" ht="28" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="28" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:7">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="28" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="28" spans="1:7">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:7">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="28" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="28" spans="1:7">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="28" spans="1:7">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" ht="28" spans="1:7">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="28" spans="1:7">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" ht="28" spans="1:7">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" ht="42" spans="1:7">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" ht="42" spans="1:7">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" ht="42" spans="1:7">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" ht="42" spans="1:7">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" ht="28" spans="1:7">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>-1</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" ht="28" spans="1:7">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>2</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" ht="42" spans="1:7">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="24" ht="42" spans="1:7">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="25" ht="42" spans="1:7">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" ht="42" spans="1:7">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
@@ -6191,13 +6900,13 @@
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="5"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
-    <col min="2" max="6" width="18" customWidth="1"/>
+    <col min="2" max="7" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6208,65 +6917,432 @@
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>227</v>
+        <v>246</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="28" spans="1:6">
+    <row r="2" ht="42" spans="1:7">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D2" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="D2" s="2">
+        <v>1</v>
+      </c>
       <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" customFormat="1" ht="28" spans="1:6">
+    <row r="3" customFormat="1" ht="42" spans="1:7">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D3" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="D3" s="2">
+        <v>1</v>
+      </c>
       <c r="E3" s="2">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="28" spans="1:6">
+    <row r="4" customFormat="1" ht="42" spans="1:7">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="2">
+        <v>2</v>
+      </c>
+      <c r="E4" s="2">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" ht="42" spans="1:7">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="42" spans="1:7">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" ht="42" spans="1:7">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" ht="42" spans="1:7">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8" s="2">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" ht="42" spans="1:7">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9" s="2">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" ht="42" spans="1:7">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" ht="42" spans="1:7">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11">
+        <v>5</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0</v>
+      </c>
+      <c r="F11" s="2">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" ht="42" spans="1:7">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12">
+        <v>6</v>
+      </c>
+      <c r="E12" s="2">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" ht="42" spans="1:7">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13">
+        <v>6</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0</v>
+      </c>
+      <c r="F13" s="2">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="28" spans="1:7">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="28" spans="1:7">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="28" spans="1:7">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16">
+        <v>7</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="42" spans="1:7">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="42" spans="1:7">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="42" spans="1:7">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="42" spans="1:7">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -6309,10 +7385,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2">
@@ -6327,10 +7403,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>248</v>
+        <v>283</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>247</v>
+        <v>282</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2">
@@ -6380,14 +7456,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>249</v>
+        <v>284</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>32</v>
@@ -6398,10 +7474,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>252</v>
+        <v>287</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -6449,14 +7525,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>32</v>
@@ -6467,10 +7543,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>256</v>
+        <v>291</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>254</v>
+        <v>289</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -6518,14 +7594,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>257</v>
+        <v>292</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>259</v>
+        <v>294</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>32</v>
@@ -6536,10 +7612,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>258</v>
+        <v>293</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -6587,14 +7663,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>261</v>
+        <v>296</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D2" s="2"/>
       <c r="E2" s="2" t="s">
-        <v>262</v>
+        <v>297</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>32</v>
@@ -6605,10 +7681,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>263</v>
+        <v>298</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>250</v>
+        <v>285</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -6886,7 +7962,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
@@ -7050,6 +8126,23 @@
         <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7062,7 +8155,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
@@ -7093,10 +8186,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D2" s="2">
         <v>0.1</v>
@@ -7113,10 +8206,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="D3">
         <v>0.1</v>
@@ -7130,10 +8223,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4">
         <v>0.009</v>
@@ -7147,10 +8240,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5">
         <v>1.51</v>
@@ -7164,10 +8257,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6">
         <v>0.111</v>
@@ -7181,10 +8274,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>49</v>
@@ -7198,10 +8291,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>50</v>
@@ -7215,15 +8308,32 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
@@ -7236,7 +8346,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="6" width="18" customWidth="1"/>
@@ -7267,10 +8377,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D2" s="2">
         <v>0.1</v>
@@ -7287,10 +8397,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="D3">
         <v>0.1</v>
@@ -7304,10 +8414,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D4">
         <v>0.009</v>
@@ -7321,10 +8431,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5">
         <v>1.51</v>
@@ -7338,10 +8448,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D6">
         <v>0.111</v>
@@ -7355,10 +8465,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>49</v>
@@ -7372,10 +8482,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>50</v>
@@ -7389,15 +8499,32 @@
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" ht="28" spans="1:6">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
     </row>
